--- a/data/5822_Chandan_CapitalStructure_Workings.xlsx
+++ b/data/5822_Chandan_CapitalStructure_Workings.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Data collected by</t>
   </si>
   <si>
-    <t xml:space="preserve">Chandan &amp; Piyush: KPR Mill, Welspun Living, Indo Count  |  Nikhilranjan: Vardhman, Trident, Arvind  |  Prantik: Nitin Spinners, Sutlej  |  Gravit: Gokaldas, Siyaram</t>
+    <t xml:space="preserve">Chandan: KPR Mill, Welspun Living  |  Piyush: Indo Count, Vardhman  |  Nikhilranjan: Trident, Arvind  |  Prantik: Nitin Spinners, Sutlej  |  Gravit: Gokaldas, Siyaram  (two companies each)</t>
   </si>
   <si>
     <t xml:space="preserve">Code &amp; data (GitHub)</t>
